--- a/data/trans_dic/P79$ninguna_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79$ninguna_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,18; 99,06</t>
+          <t>93,69; 98,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,78; 99,48</t>
+          <t>93,97; 99,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,68; 99,0</t>
+          <t>95,38; 98,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,48; 92,14</t>
+          <t>84,74; 91,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,81; 93,3</t>
+          <t>88,29; 93,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,53; 91,97</t>
+          <t>87,6; 91,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,31; 97,23</t>
+          <t>90,98; 96,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,92; 95,45</t>
+          <t>90,41; 95,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,08; 95,66</t>
+          <t>91,9; 95,45</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,89; 92,8</t>
+          <t>81,26; 91,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,17; 94,16</t>
+          <t>86,13; 92,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,62; 93,07</t>
+          <t>85,1; 91,13</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96,45; 99,49</t>
+          <t>96,62; 99,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96,8; 99,33</t>
+          <t>95,58; 98,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,26; 99,19</t>
+          <t>96,88; 98,93</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,55; 97,63</t>
+          <t>91,29; 96,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,66; 96,64</t>
+          <t>90,73; 96,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,32; 96,66</t>
+          <t>91,93; 95,65</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93,36; 97,02</t>
+          <t>93,12; 96,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,94</t>
+          <t>87,53; 91,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,11; 96,24</t>
+          <t>90,98; 93,76</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>61,59%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>60,61; 85,01</t>
+          <t>57,58; 65,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,28; 64,8</t>
+          <t>58,56; 64,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60,82; 81,2</t>
+          <t>59,35; 64,01</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,06; 90,44</t>
+          <t>84,61; 87,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86,01; 89,4</t>
+          <t>84,46; 86,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,36; 89,15</t>
+          <t>84,93; 86,58</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>294199</t>
+          <t>301432</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>276390</t>
+          <t>302593</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>570589</t>
+          <t>604026</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>276741; 300638</t>
+          <t>290219; 306574</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>257193; 281843</t>
+          <t>290408; 306553</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>549737; 580947</t>
+          <t>590234; 611829</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>448110</t>
+          <t>459610</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>458538</t>
+          <t>485727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>906648</t>
+          <t>945337</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>426926; 465634</t>
+          <t>438993; 476015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>445901; 468476</t>
+          <t>470590; 496574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>881778; 926538</t>
+          <t>920694; 964318</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>296627</t>
+          <t>294144</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>313096</t>
+          <t>319702</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609723</t>
+          <t>613846</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>287893; 303231</t>
+          <t>284055; 301338</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>302043; 320622</t>
+          <t>309887; 326884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>596489; 619692</t>
+          <t>601917; 625184</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>265398</t>
+          <t>308120</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>350001</t>
+          <t>354687</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615400</t>
+          <t>662807</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>246948; 276468</t>
+          <t>286829; 323372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>337047; 359917</t>
+          <t>339534; 365397</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>595952; 633079</t>
+          <t>635853; 680928</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>174135</t>
+          <t>199317</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>249783</t>
+          <t>219057</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>423918</t>
+          <t>418374</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>170277; 175647</t>
+          <t>195128; 201347</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>245576; 252006</t>
+          <t>214467; 221679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>418461; 426777</t>
+          <t>413038; 421774</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>253573</t>
+          <t>250026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240510</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>494083</t>
+          <t>494224</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>244852; 258299</t>
+          <t>241885; 255925</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233098; 245756</t>
+          <t>236334; 250082</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>484218; 501544</t>
+          <t>483051; 502576</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>561813</t>
+          <t>647412</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>760531</t>
+          <t>659733</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1322343</t>
+          <t>1307145</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>550026; 571609</t>
+          <t>633620; 657652</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>733566; 793665</t>
+          <t>642563; 673792</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1296869; 1354950</t>
+          <t>1287018; 1326336</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>660035</t>
+          <t>479572</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>425470</t>
+          <t>494518</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1085506</t>
+          <t>974090</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>554712; 778010</t>
+          <t>449431; 508044</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>402581; 447619</t>
+          <t>469074; 517187</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>976794; 1304035</t>
+          <t>938712; 1012295</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2953890</t>
+          <t>2939631</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3074321</t>
+          <t>3080217</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6028210</t>
+          <t>6019848</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2895118; 3042585</t>
+          <t>2894495; 2985086</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3028389; 3148028</t>
+          <t>3039780; 3117324</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5945894; 6138405</t>
+          <t>5961646; 6077518</t>
         </is>
       </c>
     </row>
